--- a/order_management/24.13-move-change-show-functionality/24.13 - Move-Change Show functionality.xlsx
+++ b/order_management/24.13-move-change-show-functionality/24.13 - Move-Change Show functionality.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Endpoints" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Open Questions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Cross-Epic Dependencies" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Implementation Status" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$K$11</definedName>
@@ -112,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -153,6 +154,10 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -518,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -657,6 +662,54 @@
       </c>
       <c r="B13" s="8" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Not started — analysis only</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Impl Branch</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Impl Commits</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -670,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -684,6 +737,7 @@
     <col width="48" customWidth="1" min="9" max="9"/>
     <col width="62" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -742,6 +796,11 @@
           <t>Confluence</t>
         </is>
       </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Impl Status (2026-07-01)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -791,6 +850,11 @@
           <t>Open §Order Management → Story 24.13</t>
         </is>
       </c>
+      <c r="L2" s="14" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -840,6 +904,11 @@
           <t>Open §Order Management → Story 24.13</t>
         </is>
       </c>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -889,6 +958,11 @@
           <t>Open §Order Management → Story 24.13</t>
         </is>
       </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -938,6 +1012,11 @@
           <t>Open §Order Management → Story 24.13</t>
         </is>
       </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -989,6 +1068,11 @@
       <c r="K6" s="10" t="inlineStr">
         <is>
           <t>Open §Order Management → Story 24.13</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
         </is>
       </c>
     </row>
@@ -1040,6 +1124,11 @@
           <t>Open §Order Management → Story 24.13</t>
         </is>
       </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1089,6 +1178,11 @@
           <t>Open §Order Management → Story 24.13</t>
         </is>
       </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1142,6 +1236,11 @@
           <t>Open §Order Management → Story 24.13</t>
         </is>
       </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1193,6 +1292,11 @@
       <c r="K10" s="10" t="inlineStr">
         <is>
           <t>Open §Order Management → Story 24.13</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
         </is>
       </c>
     </row>
@@ -1242,6 +1346,11 @@
       <c r="K11" s="10" t="inlineStr">
         <is>
           <t>Open §Order Management → Story 24.13</t>
+        </is>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>Out of Scope — —</t>
         </is>
       </c>
     </row>
@@ -1363,11 +1472,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1381,6 +1492,16 @@
           <t>Open Question</t>
         </is>
       </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Resolution / Decision</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -1391,6 +1512,16 @@
           <t>On a successful move, are the order's financials re-priced to the destination show's ShowProduct prices (which differ per show via sales_price/actual_price) or kept frozen at the original order totals? The spec mandates 'no modification' but is silent on price impact.</t>
         </is>
       </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>[OPEN — for team discussion]</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Current direction (2026-07-01): lean toward keeping order totals frozen at the original values (consistent with the 'no modification' rule) — pending team confirmation.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1399,6 +1530,16 @@
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Does 'validate applicable included products' mean only an existence check (the destination show offers each included product_id) or per-show stock validation? Default-included lines carry no tracked inventory (excluded from commit; decreasing/removing never changes totals), so there is no inventory to validate against beyond existence — confirms the intended semantics for 24.13-f.</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>[OPEN — for team discussion]</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Current direction (2026-07-01): existence-only check (destination show offers each included product_id); default-included lines carry no tracked inventory, so nothing to stock-validate beyond existence — pending team confirmation.</t>
         </is>
       </c>
     </row>
@@ -1450,4 +1591,118 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Not started — analysis/feasibility stage only. No branch, no SBE ticket, no PR, no Swagger tag. Per-requirement build status is ◻ Not started.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Remaining — all in-scope</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>All 9 in-scope reqs not started: 24.13-a Move Show action, 24.13-b booth sizes, 24.13-c included products, 24.13-d no in-move edits, 24.13-e destination inventory validation, 24.13-f included-product availability (Partial), 24.13-g clear unavailable message, 24.13-h backend enforcement, 24.13-i atomic release + re-commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Open decision — re-pricing on move</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Are order financials re-priced to the destination show's ShowProduct prices or kept frozen at original totals? Current direction: frozen (consistent with 'no modification') — pending team confirmation. No code until answered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Open decision — included-product validation</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Existence check vs per-show stock validation for default-included lines (24.13-f)? Current direction: existence-only check — default-included lines carry no tracked inventory. No code until answered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Dependency — Cross-Epic</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Dependency — build-once-reuse</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>24.12's release-reservations-by-order_id helper (24.13-e/i) and 24.1's auth guard (24.13-h) are reused per Build Consolidation, not owed by this story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Out of API scope</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Front-end wiring; and 24.13-j (opening/creating floorplan inventory) — manual floorplan / show-products prerequisite.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>